--- a/Шаблон списка ЛМК+проф+ОПО — пол заполнен.xlsx
+++ b/Шаблон списка ЛМК+проф+ОПО — пол заполнен.xlsx
@@ -1019,7 +1019,11 @@
           <t>057-674-399 10</t>
         </is>
       </c>
-      <c r="E3" s="49" t="n"/>
+      <c r="E3" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F3" s="50" t="n"/>
       <c r="G3" s="51" t="inlineStr">
         <is>
@@ -1107,7 +1111,11 @@
           <t>128-926-784 08</t>
         </is>
       </c>
-      <c r="E4" s="49" t="n"/>
+      <c r="E4" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F4" s="50" t="n"/>
       <c r="G4" s="51" t="inlineStr">
         <is>
@@ -1195,7 +1203,11 @@
           <t>043-232-856 27</t>
         </is>
       </c>
-      <c r="E5" s="49" t="n"/>
+      <c r="E5" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F5" s="50" t="n"/>
       <c r="G5" s="51" t="inlineStr">
         <is>
@@ -1283,7 +1295,11 @@
           <t>125-758-954 99</t>
         </is>
       </c>
-      <c r="E6" s="49" t="n"/>
+      <c r="E6" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F6" s="50" t="n"/>
       <c r="G6" s="51" t="inlineStr">
         <is>
@@ -1371,7 +1387,11 @@
           <t>103-806-826 35</t>
         </is>
       </c>
-      <c r="E7" s="49" t="n"/>
+      <c r="E7" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F7" s="50" t="n"/>
       <c r="G7" s="51" t="inlineStr">
         <is>
@@ -1459,7 +1479,11 @@
           <t>034-133-939 26</t>
         </is>
       </c>
-      <c r="E8" s="49" t="n"/>
+      <c r="E8" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F8" s="50" t="n"/>
       <c r="G8" s="51" t="inlineStr">
         <is>
@@ -1547,7 +1571,11 @@
           <t>049-064-561 68</t>
         </is>
       </c>
-      <c r="E9" s="49" t="n"/>
+      <c r="E9" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F9" s="50" t="n"/>
       <c r="G9" s="51" t="inlineStr">
         <is>
@@ -1635,7 +1663,11 @@
           <t>046-350-338 39</t>
         </is>
       </c>
-      <c r="E10" s="49" t="n"/>
+      <c r="E10" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F10" s="50" t="n"/>
       <c r="G10" s="51" t="inlineStr">
         <is>
@@ -1723,7 +1755,11 @@
           <t>187-761-470 22</t>
         </is>
       </c>
-      <c r="E11" s="49" t="n"/>
+      <c r="E11" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F11" s="50" t="n"/>
       <c r="G11" s="51" t="inlineStr">
         <is>
@@ -1811,7 +1847,11 @@
           <t>114-432-703 15</t>
         </is>
       </c>
-      <c r="E12" s="49" t="n"/>
+      <c r="E12" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F12" s="50" t="n"/>
       <c r="G12" s="51" t="inlineStr">
         <is>
@@ -1899,7 +1939,11 @@
           <t>032-468-611 44</t>
         </is>
       </c>
-      <c r="E13" s="49" t="n"/>
+      <c r="E13" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F13" s="50" t="n"/>
       <c r="G13" s="51" t="inlineStr">
         <is>
@@ -1987,7 +2031,11 @@
           <t>079-146-474 98</t>
         </is>
       </c>
-      <c r="E14" s="49" t="n"/>
+      <c r="E14" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F14" s="50" t="n"/>
       <c r="G14" s="51" t="inlineStr">
         <is>
@@ -2075,7 +2123,11 @@
           <t>023-212-021 67</t>
         </is>
       </c>
-      <c r="E15" s="49" t="n"/>
+      <c r="E15" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F15" s="50" t="n"/>
       <c r="G15" s="51" t="inlineStr">
         <is>
@@ -2163,7 +2215,11 @@
           <t>004-357-971 40</t>
         </is>
       </c>
-      <c r="E16" s="49" t="n"/>
+      <c r="E16" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F16" s="50" t="n"/>
       <c r="G16" s="51" t="inlineStr">
         <is>
@@ -2251,7 +2307,11 @@
           <t>080-112-510 00</t>
         </is>
       </c>
-      <c r="E17" s="49" t="n"/>
+      <c r="E17" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F17" s="50" t="n"/>
       <c r="G17" s="51" t="inlineStr">
         <is>
@@ -2339,7 +2399,11 @@
           <t>048-285-251 76</t>
         </is>
       </c>
-      <c r="E18" s="49" t="n"/>
+      <c r="E18" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F18" s="50" t="n"/>
       <c r="G18" s="51" t="inlineStr">
         <is>
@@ -2427,7 +2491,11 @@
           <t>068-669-037 17</t>
         </is>
       </c>
-      <c r="E19" s="49" t="n"/>
+      <c r="E19" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F19" s="50" t="n"/>
       <c r="G19" s="51" t="inlineStr">
         <is>
@@ -2515,7 +2583,11 @@
           <t>126-638-025 58</t>
         </is>
       </c>
-      <c r="E20" s="49" t="n"/>
+      <c r="E20" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F20" s="50" t="n"/>
       <c r="G20" s="51" t="inlineStr">
         <is>
@@ -2603,7 +2675,11 @@
           <t>094-525-535 85</t>
         </is>
       </c>
-      <c r="E21" s="49" t="n"/>
+      <c r="E21" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F21" s="50" t="n"/>
       <c r="G21" s="51" t="inlineStr">
         <is>
@@ -2691,7 +2767,11 @@
           <t>185-050-199 62</t>
         </is>
       </c>
-      <c r="E22" s="49" t="n"/>
+      <c r="E22" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F22" s="50" t="n"/>
       <c r="G22" s="51" t="inlineStr">
         <is>
@@ -2779,7 +2859,11 @@
           <t>015-826-776 65</t>
         </is>
       </c>
-      <c r="E23" s="49" t="n"/>
+      <c r="E23" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F23" s="50" t="n"/>
       <c r="G23" s="51" t="inlineStr">
         <is>
@@ -2867,7 +2951,11 @@
           <t>124-975-726 92</t>
         </is>
       </c>
-      <c r="E24" s="49" t="n"/>
+      <c r="E24" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F24" s="50" t="n"/>
       <c r="G24" s="51" t="inlineStr">
         <is>
@@ -2955,7 +3043,11 @@
           <t>119-780-403 76</t>
         </is>
       </c>
-      <c r="E25" s="49" t="n"/>
+      <c r="E25" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F25" s="50" t="n"/>
       <c r="G25" s="51" t="inlineStr">
         <is>
@@ -3043,7 +3135,11 @@
           <t>022-469-805 48</t>
         </is>
       </c>
-      <c r="E26" s="49" t="n"/>
+      <c r="E26" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F26" s="50" t="n"/>
       <c r="G26" s="51" t="inlineStr">
         <is>
@@ -3131,7 +3227,11 @@
           <t>014-881-954 68</t>
         </is>
       </c>
-      <c r="E27" s="49" t="n"/>
+      <c r="E27" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F27" s="50" t="n"/>
       <c r="G27" s="51" t="inlineStr">
         <is>
@@ -3219,7 +3319,11 @@
           <t>001-946-406 22</t>
         </is>
       </c>
-      <c r="E28" s="49" t="n"/>
+      <c r="E28" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F28" s="50" t="n"/>
       <c r="G28" s="51" t="inlineStr">
         <is>
@@ -3307,7 +3411,11 @@
           <t>193-398-956 38</t>
         </is>
       </c>
-      <c r="E29" s="49" t="n"/>
+      <c r="E29" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F29" s="50" t="n"/>
       <c r="G29" s="51" t="inlineStr">
         <is>
@@ -3395,7 +3503,11 @@
           <t>001-024-618 61</t>
         </is>
       </c>
-      <c r="E30" s="49" t="n"/>
+      <c r="E30" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F30" s="50" t="n"/>
       <c r="G30" s="51" t="inlineStr">
         <is>
@@ -3483,7 +3595,11 @@
           <t>005-308-630 08</t>
         </is>
       </c>
-      <c r="E31" s="49" t="n"/>
+      <c r="E31" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F31" s="50" t="n"/>
       <c r="G31" s="51" t="inlineStr">
         <is>
@@ -3571,7 +3687,11 @@
           <t>139-113-351 38</t>
         </is>
       </c>
-      <c r="E32" s="49" t="n"/>
+      <c r="E32" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F32" s="50" t="n"/>
       <c r="G32" s="51" t="inlineStr">
         <is>
@@ -3659,7 +3779,11 @@
           <t>136-604-917 62</t>
         </is>
       </c>
-      <c r="E33" s="49" t="n"/>
+      <c r="E33" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F33" s="50" t="n"/>
       <c r="G33" s="51" t="inlineStr">
         <is>
@@ -3747,7 +3871,11 @@
           <t>125-426-379 49</t>
         </is>
       </c>
-      <c r="E34" s="49" t="n"/>
+      <c r="E34" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F34" s="50" t="n"/>
       <c r="G34" s="51" t="inlineStr">
         <is>
@@ -3835,7 +3963,11 @@
           <t>210-350-970 09</t>
         </is>
       </c>
-      <c r="E35" s="49" t="n"/>
+      <c r="E35" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F35" s="50" t="n"/>
       <c r="G35" s="51" t="inlineStr">
         <is>
@@ -3923,7 +4055,11 @@
           <t>020-391-812 10</t>
         </is>
       </c>
-      <c r="E36" s="49" t="n"/>
+      <c r="E36" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F36" s="50" t="n"/>
       <c r="G36" s="51" t="inlineStr">
         <is>
@@ -4011,7 +4147,11 @@
           <t>083-981-603 02</t>
         </is>
       </c>
-      <c r="E37" s="49" t="n"/>
+      <c r="E37" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F37" s="50" t="n"/>
       <c r="G37" s="51" t="inlineStr">
         <is>
@@ -4099,7 +4239,11 @@
           <t>144-132-917 33</t>
         </is>
       </c>
-      <c r="E38" s="49" t="n"/>
+      <c r="E38" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F38" s="50" t="n"/>
       <c r="G38" s="51" t="inlineStr">
         <is>
@@ -4187,7 +4331,11 @@
           <t>005-503-166 98</t>
         </is>
       </c>
-      <c r="E39" s="49" t="n"/>
+      <c r="E39" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F39" s="50" t="n"/>
       <c r="G39" s="51" t="inlineStr">
         <is>
@@ -4275,7 +4423,11 @@
           <t>010-143-907 80</t>
         </is>
       </c>
-      <c r="E40" s="49" t="n"/>
+      <c r="E40" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F40" s="50" t="n"/>
       <c r="G40" s="51" t="inlineStr">
         <is>
@@ -4363,7 +4515,11 @@
           <t>001-946-559 38</t>
         </is>
       </c>
-      <c r="E41" s="49" t="n"/>
+      <c r="E41" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F41" s="50" t="n"/>
       <c r="G41" s="51" t="inlineStr">
         <is>
@@ -4451,7 +4607,11 @@
           <t>135-859-904 06</t>
         </is>
       </c>
-      <c r="E42" s="49" t="n"/>
+      <c r="E42" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F42" s="50" t="n"/>
       <c r="G42" s="51" t="inlineStr">
         <is>
@@ -4539,7 +4699,11 @@
           <t>024-274-750 37</t>
         </is>
       </c>
-      <c r="E43" s="49" t="n"/>
+      <c r="E43" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F43" s="50" t="n"/>
       <c r="G43" s="51" t="inlineStr">
         <is>
@@ -4627,7 +4791,11 @@
           <t>046-587-145 87</t>
         </is>
       </c>
-      <c r="E44" s="49" t="n"/>
+      <c r="E44" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F44" s="50" t="n"/>
       <c r="G44" s="51" t="inlineStr">
         <is>
@@ -4715,7 +4883,11 @@
           <t>007-748-523 64</t>
         </is>
       </c>
-      <c r="E45" s="49" t="n"/>
+      <c r="E45" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F45" s="50" t="n"/>
       <c r="G45" s="51" t="inlineStr">
         <is>
@@ -4803,7 +4975,11 @@
           <t>136-335-182 48</t>
         </is>
       </c>
-      <c r="E46" s="49" t="n"/>
+      <c r="E46" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F46" s="50" t="n"/>
       <c r="G46" s="51" t="inlineStr">
         <is>
@@ -4891,7 +5067,11 @@
           <t>194-624-665 04</t>
         </is>
       </c>
-      <c r="E47" s="49" t="n"/>
+      <c r="E47" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F47" s="50" t="n"/>
       <c r="G47" s="51" t="inlineStr">
         <is>
@@ -4979,7 +5159,11 @@
           <t>007-748-524 65</t>
         </is>
       </c>
-      <c r="E48" s="49" t="n"/>
+      <c r="E48" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F48" s="50" t="n"/>
       <c r="G48" s="51" t="inlineStr">
         <is>
@@ -5067,7 +5251,11 @@
           <t>221-741-613 29</t>
         </is>
       </c>
-      <c r="E49" s="49" t="n"/>
+      <c r="E49" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F49" s="50" t="n"/>
       <c r="G49" s="51" t="inlineStr">
         <is>
@@ -5155,7 +5343,11 @@
           <t>026-872-766 87</t>
         </is>
       </c>
-      <c r="E50" s="49" t="n"/>
+      <c r="E50" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F50" s="50" t="n"/>
       <c r="G50" s="51" t="inlineStr">
         <is>
@@ -5243,7 +5435,11 @@
           <t>165-479-892 29</t>
         </is>
       </c>
-      <c r="E51" s="49" t="n"/>
+      <c r="E51" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F51" s="50" t="n"/>
       <c r="G51" s="51" t="inlineStr">
         <is>
@@ -5331,7 +5527,11 @@
           <t>140-734-085 34</t>
         </is>
       </c>
-      <c r="E52" s="49" t="n"/>
+      <c r="E52" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F52" s="50" t="n"/>
       <c r="G52" s="51" t="inlineStr">
         <is>
@@ -5419,7 +5619,11 @@
           <t>167-946-540 25</t>
         </is>
       </c>
-      <c r="E53" s="49" t="n"/>
+      <c r="E53" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F53" s="50" t="n"/>
       <c r="G53" s="51" t="inlineStr">
         <is>
@@ -5507,7 +5711,11 @@
           <t>188-742-387 29</t>
         </is>
       </c>
-      <c r="E54" s="49" t="n"/>
+      <c r="E54" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F54" s="50" t="n"/>
       <c r="G54" s="51" t="inlineStr">
         <is>
@@ -5595,7 +5803,11 @@
           <t>001-549-740 21</t>
         </is>
       </c>
-      <c r="E55" s="49" t="n"/>
+      <c r="E55" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F55" s="50" t="n"/>
       <c r="G55" s="51" t="inlineStr">
         <is>
@@ -5683,7 +5895,11 @@
           <t>157-905-167 93</t>
         </is>
       </c>
-      <c r="E56" s="49" t="n"/>
+      <c r="E56" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F56" s="50" t="n"/>
       <c r="G56" s="51" t="inlineStr">
         <is>
@@ -5771,7 +5987,11 @@
           <t>149-980-959 42</t>
         </is>
       </c>
-      <c r="E57" s="49" t="n"/>
+      <c r="E57" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F57" s="50" t="n"/>
       <c r="G57" s="51" t="inlineStr">
         <is>
@@ -5859,7 +6079,11 @@
           <t>193-344-670 87</t>
         </is>
       </c>
-      <c r="E58" s="49" t="n"/>
+      <c r="E58" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F58" s="50" t="n"/>
       <c r="G58" s="51" t="inlineStr">
         <is>
@@ -5947,7 +6171,11 @@
           <t>151-145-322 16</t>
         </is>
       </c>
-      <c r="E59" s="49" t="n"/>
+      <c r="E59" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F59" s="50" t="n"/>
       <c r="G59" s="51" t="inlineStr">
         <is>
@@ -6035,7 +6263,11 @@
           <t>138-513-714 62</t>
         </is>
       </c>
-      <c r="E60" s="49" t="n"/>
+      <c r="E60" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F60" s="50" t="n"/>
       <c r="G60" s="51" t="inlineStr">
         <is>
@@ -6123,7 +6355,11 @@
           <t>128-866-839 20</t>
         </is>
       </c>
-      <c r="E61" s="49" t="n"/>
+      <c r="E61" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F61" s="50" t="n"/>
       <c r="G61" s="51" t="inlineStr">
         <is>
@@ -6211,7 +6447,11 @@
           <t>150-514-561 27</t>
         </is>
       </c>
-      <c r="E62" s="49" t="n"/>
+      <c r="E62" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F62" s="50" t="n"/>
       <c r="G62" s="51" t="inlineStr">
         <is>
@@ -6299,7 +6539,11 @@
           <t>013-505-131 89</t>
         </is>
       </c>
-      <c r="E63" s="49" t="n"/>
+      <c r="E63" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F63" s="50" t="n"/>
       <c r="G63" s="51" t="inlineStr">
         <is>
@@ -6387,7 +6631,11 @@
           <t>108-330-307 13</t>
         </is>
       </c>
-      <c r="E64" s="49" t="n"/>
+      <c r="E64" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F64" s="50" t="n"/>
       <c r="G64" s="51" t="inlineStr">
         <is>
@@ -6475,7 +6723,11 @@
           <t>043-924-645 63</t>
         </is>
       </c>
-      <c r="E65" s="49" t="n"/>
+      <c r="E65" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F65" s="50" t="n"/>
       <c r="G65" s="51" t="inlineStr">
         <is>
@@ -6563,7 +6815,11 @@
           <t>018-261-947 51</t>
         </is>
       </c>
-      <c r="E66" s="49" t="n"/>
+      <c r="E66" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F66" s="50" t="n"/>
       <c r="G66" s="51" t="inlineStr">
         <is>
@@ -6651,7 +6907,11 @@
           <t>119-885-518 11</t>
         </is>
       </c>
-      <c r="E67" s="49" t="n"/>
+      <c r="E67" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F67" s="50" t="n"/>
       <c r="G67" s="51" t="inlineStr">
         <is>
@@ -6739,7 +6999,11 @@
           <t>095-183-086 86</t>
         </is>
       </c>
-      <c r="E68" s="49" t="n"/>
+      <c r="E68" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F68" s="50" t="n"/>
       <c r="G68" s="51" t="inlineStr">
         <is>
@@ -6827,7 +7091,11 @@
           <t>058-429-200 71</t>
         </is>
       </c>
-      <c r="E69" s="49" t="n"/>
+      <c r="E69" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F69" s="50" t="n"/>
       <c r="G69" s="51" t="inlineStr">
         <is>
@@ -6915,7 +7183,11 @@
           <t>036-392-199 66</t>
         </is>
       </c>
-      <c r="E70" s="49" t="n"/>
+      <c r="E70" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F70" s="50" t="n"/>
       <c r="G70" s="51" t="inlineStr">
         <is>
@@ -7003,7 +7275,11 @@
           <t>116-987-951 17</t>
         </is>
       </c>
-      <c r="E71" s="49" t="n"/>
+      <c r="E71" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F71" s="50" t="n"/>
       <c r="G71" s="51" t="inlineStr">
         <is>
@@ -7091,7 +7367,11 @@
           <t>065-048-140 45</t>
         </is>
       </c>
-      <c r="E72" s="49" t="n"/>
+      <c r="E72" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F72" s="50" t="n"/>
       <c r="G72" s="51" t="inlineStr">
         <is>
@@ -7179,7 +7459,11 @@
           <t>142-240-380 11</t>
         </is>
       </c>
-      <c r="E73" s="49" t="n"/>
+      <c r="E73" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F73" s="50" t="n"/>
       <c r="G73" s="51" t="inlineStr">
         <is>
@@ -7267,7 +7551,11 @@
           <t>145-858-529 07</t>
         </is>
       </c>
-      <c r="E74" s="49" t="n"/>
+      <c r="E74" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F74" s="50" t="n"/>
       <c r="G74" s="51" t="inlineStr">
         <is>
@@ -7355,7 +7643,11 @@
           <t>125-706-271 46</t>
         </is>
       </c>
-      <c r="E75" s="49" t="n"/>
+      <c r="E75" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F75" s="50" t="n"/>
       <c r="G75" s="51" t="inlineStr">
         <is>
@@ -7443,7 +7735,11 @@
           <t>126-910-880 65</t>
         </is>
       </c>
-      <c r="E76" s="49" t="n"/>
+      <c r="E76" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F76" s="50" t="n"/>
       <c r="G76" s="51" t="inlineStr">
         <is>
@@ -7531,7 +7827,11 @@
           <t>084-319-031 57</t>
         </is>
       </c>
-      <c r="E77" s="49" t="n"/>
+      <c r="E77" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F77" s="50" t="n"/>
       <c r="G77" s="51" t="inlineStr">
         <is>
@@ -7619,7 +7919,11 @@
           <t>171-161-045 24</t>
         </is>
       </c>
-      <c r="E78" s="49" t="n"/>
+      <c r="E78" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F78" s="50" t="n"/>
       <c r="G78" s="51" t="inlineStr">
         <is>
@@ -7707,7 +8011,11 @@
           <t>209-966-113 96</t>
         </is>
       </c>
-      <c r="E79" s="49" t="n"/>
+      <c r="E79" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F79" s="50" t="n"/>
       <c r="G79" s="51" t="inlineStr">
         <is>
@@ -7795,7 +8103,11 @@
           <t>077-644-645 06</t>
         </is>
       </c>
-      <c r="E80" s="49" t="n"/>
+      <c r="E80" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F80" s="50" t="n"/>
       <c r="G80" s="51" t="inlineStr">
         <is>
@@ -7883,7 +8195,11 @@
           <t>004-922-399 35</t>
         </is>
       </c>
-      <c r="E81" s="49" t="n"/>
+      <c r="E81" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F81" s="50" t="n"/>
       <c r="G81" s="51" t="inlineStr">
         <is>
@@ -7979,7 +8295,11 @@
           <t>173-721-383 69</t>
         </is>
       </c>
-      <c r="E82" s="49" t="n"/>
+      <c r="E82" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F82" s="50" t="n"/>
       <c r="G82" s="51" t="inlineStr">
         <is>
@@ -8075,7 +8395,11 @@
           <t>048-246-089 68</t>
         </is>
       </c>
-      <c r="E83" s="49" t="n"/>
+      <c r="E83" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F83" s="50" t="n"/>
       <c r="G83" s="51" t="inlineStr">
         <is>
@@ -8171,7 +8495,11 @@
           <t>005-174-739 27</t>
         </is>
       </c>
-      <c r="E84" s="49" t="n"/>
+      <c r="E84" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F84" s="50" t="n"/>
       <c r="G84" s="51" t="inlineStr">
         <is>
@@ -8267,7 +8595,11 @@
           <t>023-728-201 27</t>
         </is>
       </c>
-      <c r="E85" s="49" t="n"/>
+      <c r="E85" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F85" s="50" t="n"/>
       <c r="G85" s="51" t="inlineStr">
         <is>
@@ -8363,7 +8695,11 @@
           <t>132-461-481 33</t>
         </is>
       </c>
-      <c r="E86" s="49" t="n"/>
+      <c r="E86" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F86" s="50" t="n"/>
       <c r="G86" s="51" t="inlineStr">
         <is>
@@ -8459,7 +8795,11 @@
           <t>055-410-989 55</t>
         </is>
       </c>
-      <c r="E87" s="49" t="n"/>
+      <c r="E87" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F87" s="50" t="n"/>
       <c r="G87" s="51" t="inlineStr">
         <is>
@@ -8555,7 +8895,11 @@
           <t>065-715-189 77</t>
         </is>
       </c>
-      <c r="E88" s="49" t="n"/>
+      <c r="E88" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F88" s="50" t="n"/>
       <c r="G88" s="51" t="inlineStr">
         <is>
@@ -8651,7 +8995,11 @@
           <t>078-244-872 99</t>
         </is>
       </c>
-      <c r="E89" s="49" t="n"/>
+      <c r="E89" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F89" s="50" t="n"/>
       <c r="G89" s="51" t="inlineStr">
         <is>
@@ -8747,7 +9095,11 @@
           <t>056-122-002 07</t>
         </is>
       </c>
-      <c r="E90" s="49" t="n"/>
+      <c r="E90" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F90" s="50" t="n"/>
       <c r="G90" s="51" t="inlineStr">
         <is>
@@ -8835,7 +9187,11 @@
           <t>146-226-387 60</t>
         </is>
       </c>
-      <c r="E91" s="49" t="n"/>
+      <c r="E91" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F91" s="50" t="n"/>
       <c r="G91" s="51" t="inlineStr">
         <is>
@@ -8923,7 +9279,11 @@
           <t>063-210-456 13</t>
         </is>
       </c>
-      <c r="E92" s="49" t="n"/>
+      <c r="E92" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F92" s="50" t="n"/>
       <c r="G92" s="51" t="inlineStr">
         <is>
@@ -9011,7 +9371,11 @@
           <t>045-075-814 51</t>
         </is>
       </c>
-      <c r="E93" s="49" t="n"/>
+      <c r="E93" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F93" s="50" t="n"/>
       <c r="G93" s="51" t="inlineStr">
         <is>
@@ -9099,7 +9463,11 @@
           <t>172-727-596 97</t>
         </is>
       </c>
-      <c r="E94" s="49" t="n"/>
+      <c r="E94" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F94" s="50" t="n"/>
       <c r="G94" s="51" t="inlineStr">
         <is>
@@ -9187,7 +9555,11 @@
           <t>175-923-904 05</t>
         </is>
       </c>
-      <c r="E95" s="49" t="n"/>
+      <c r="E95" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F95" s="50" t="n"/>
       <c r="G95" s="51" t="inlineStr">
         <is>
@@ -9275,7 +9647,11 @@
           <t>068-646-413 00</t>
         </is>
       </c>
-      <c r="E96" s="49" t="n"/>
+      <c r="E96" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F96" s="50" t="n"/>
       <c r="G96" s="51" t="inlineStr">
         <is>
@@ -9363,7 +9739,11 @@
           <t>105-950-943 60</t>
         </is>
       </c>
-      <c r="E97" s="49" t="n"/>
+      <c r="E97" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F97" s="50" t="n"/>
       <c r="G97" s="51" t="inlineStr">
         <is>
@@ -9451,7 +9831,11 @@
           <t>154-812-410 51</t>
         </is>
       </c>
-      <c r="E98" s="49" t="n"/>
+      <c r="E98" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F98" s="50" t="n"/>
       <c r="G98" s="51" t="inlineStr">
         <is>
@@ -9539,7 +9923,11 @@
           <t>110-039-153 84</t>
         </is>
       </c>
-      <c r="E99" s="49" t="n"/>
+      <c r="E99" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F99" s="50" t="n"/>
       <c r="G99" s="51" t="inlineStr">
         <is>
@@ -9627,7 +10015,11 @@
           <t>115-043-181 03</t>
         </is>
       </c>
-      <c r="E100" s="49" t="n"/>
+      <c r="E100" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F100" s="50" t="n"/>
       <c r="G100" s="51" t="inlineStr">
         <is>
@@ -9715,7 +10107,11 @@
           <t>152-324-399 42</t>
         </is>
       </c>
-      <c r="E101" s="49" t="n"/>
+      <c r="E101" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F101" s="50" t="n"/>
       <c r="G101" s="51" t="inlineStr">
         <is>
@@ -9803,7 +10199,11 @@
           <t>166-507-435 79</t>
         </is>
       </c>
-      <c r="E102" s="49" t="n"/>
+      <c r="E102" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F102" s="50" t="n"/>
       <c r="G102" s="51" t="inlineStr">
         <is>
@@ -9891,7 +10291,11 @@
           <t>184-005-664 54</t>
         </is>
       </c>
-      <c r="E103" s="49" t="n"/>
+      <c r="E103" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F103" s="50" t="n"/>
       <c r="G103" s="51" t="inlineStr">
         <is>
@@ -9987,7 +10391,11 @@
           <t>018-959-483 08</t>
         </is>
       </c>
-      <c r="E104" s="49" t="n"/>
+      <c r="E104" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F104" s="50" t="n"/>
       <c r="G104" s="51" t="inlineStr">
         <is>
@@ -10075,7 +10483,11 @@
           <t>008-865-339 77</t>
         </is>
       </c>
-      <c r="E105" s="49" t="n"/>
+      <c r="E105" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F105" s="50" t="n"/>
       <c r="G105" s="51" t="inlineStr">
         <is>
@@ -10163,7 +10575,11 @@
           <t>134-854-450 71</t>
         </is>
       </c>
-      <c r="E106" s="49" t="n"/>
+      <c r="E106" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F106" s="50" t="n"/>
       <c r="G106" s="51" t="inlineStr">
         <is>
@@ -10251,7 +10667,11 @@
           <t>176-939-404 26</t>
         </is>
       </c>
-      <c r="E107" s="49" t="n"/>
+      <c r="E107" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F107" s="50" t="n"/>
       <c r="G107" s="51" t="inlineStr">
         <is>
@@ -10339,7 +10759,11 @@
           <t>154-183-856 74</t>
         </is>
       </c>
-      <c r="E108" s="49" t="n"/>
+      <c r="E108" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F108" s="50" t="n"/>
       <c r="G108" s="51" t="inlineStr">
         <is>
@@ -10435,7 +10859,11 @@
           <t>104-597-939 81</t>
         </is>
       </c>
-      <c r="E109" s="49" t="n"/>
+      <c r="E109" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F109" s="50" t="n"/>
       <c r="G109" s="51" t="inlineStr">
         <is>
@@ -10523,7 +10951,11 @@
           <t>118-108-755 46</t>
         </is>
       </c>
-      <c r="E110" s="49" t="n"/>
+      <c r="E110" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F110" s="50" t="n"/>
       <c r="G110" s="51" t="inlineStr">
         <is>
@@ -10611,7 +11043,11 @@
           <t>171-022-718 20</t>
         </is>
       </c>
-      <c r="E111" s="49" t="n"/>
+      <c r="E111" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F111" s="50" t="n"/>
       <c r="G111" s="51" t="inlineStr">
         <is>
@@ -10707,7 +11143,11 @@
           <t>133-655-426 56</t>
         </is>
       </c>
-      <c r="E112" s="49" t="n"/>
+      <c r="E112" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F112" s="50" t="n"/>
       <c r="G112" s="51" t="inlineStr">
         <is>
@@ -10795,7 +11235,11 @@
           <t>116-163-416 26</t>
         </is>
       </c>
-      <c r="E113" s="49" t="n"/>
+      <c r="E113" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F113" s="50" t="n"/>
       <c r="G113" s="51" t="inlineStr">
         <is>
@@ -10891,7 +11335,11 @@
           <t>168-793-135 24</t>
         </is>
       </c>
-      <c r="E114" s="49" t="n"/>
+      <c r="E114" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F114" s="50" t="n"/>
       <c r="G114" s="51" t="inlineStr">
         <is>
@@ -10979,7 +11427,11 @@
           <t>075-854-992 25</t>
         </is>
       </c>
-      <c r="E115" s="49" t="n"/>
+      <c r="E115" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F115" s="50" t="n"/>
       <c r="G115" s="51" t="inlineStr">
         <is>
@@ -11067,7 +11519,11 @@
           <t>138-565-749 05</t>
         </is>
       </c>
-      <c r="E116" s="49" t="n"/>
+      <c r="E116" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F116" s="50" t="n"/>
       <c r="G116" s="51" t="inlineStr">
         <is>
@@ -11155,7 +11611,11 @@
           <t>177-840-039 96</t>
         </is>
       </c>
-      <c r="E117" s="49" t="n"/>
+      <c r="E117" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F117" s="50" t="n"/>
       <c r="G117" s="51" t="inlineStr">
         <is>
@@ -11243,7 +11703,11 @@
           <t>175-804-278 91</t>
         </is>
       </c>
-      <c r="E118" s="49" t="n"/>
+      <c r="E118" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F118" s="50" t="n"/>
       <c r="G118" s="51" t="inlineStr">
         <is>
@@ -11331,7 +11795,11 @@
           <t>021-344-684 14</t>
         </is>
       </c>
-      <c r="E119" s="49" t="n"/>
+      <c r="E119" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F119" s="50" t="n"/>
       <c r="G119" s="51" t="inlineStr">
         <is>
@@ -11427,7 +11895,11 @@
           <t>013-828-060 30</t>
         </is>
       </c>
-      <c r="E120" s="49" t="n"/>
+      <c r="E120" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F120" s="50" t="n"/>
       <c r="G120" s="51" t="inlineStr">
         <is>
@@ -11515,7 +11987,11 @@
           <t>027-155-239 36</t>
         </is>
       </c>
-      <c r="E121" s="49" t="n"/>
+      <c r="E121" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F121" s="50" t="n"/>
       <c r="G121" s="51" t="inlineStr">
         <is>
@@ -11603,7 +12079,11 @@
           <t>125-308-387 41</t>
         </is>
       </c>
-      <c r="E122" s="49" t="n"/>
+      <c r="E122" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F122" s="50" t="n"/>
       <c r="G122" s="51" t="inlineStr">
         <is>
@@ -11691,7 +12171,11 @@
           <t>009-102-880 16</t>
         </is>
       </c>
-      <c r="E123" s="49" t="n"/>
+      <c r="E123" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F123" s="50" t="n"/>
       <c r="G123" s="51" t="inlineStr">
         <is>
@@ -11779,7 +12263,11 @@
           <t>125-643-377 57</t>
         </is>
       </c>
-      <c r="E124" s="49" t="n"/>
+      <c r="E124" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F124" s="50" t="n"/>
       <c r="G124" s="51" t="inlineStr">
         <is>
@@ -11867,7 +12355,11 @@
           <t>162-290-093 48</t>
         </is>
       </c>
-      <c r="E125" s="49" t="n"/>
+      <c r="E125" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F125" s="50" t="n"/>
       <c r="G125" s="51" t="inlineStr">
         <is>
@@ -11955,7 +12447,11 @@
           <t>178-876-680 60</t>
         </is>
       </c>
-      <c r="E126" s="49" t="n"/>
+      <c r="E126" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F126" s="50" t="n"/>
       <c r="G126" s="51" t="inlineStr">
         <is>
@@ -12043,7 +12539,11 @@
           <t>037-650-815 64</t>
         </is>
       </c>
-      <c r="E127" s="49" t="n"/>
+      <c r="E127" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F127" s="50" t="n"/>
       <c r="G127" s="51" t="inlineStr">
         <is>
@@ -12131,7 +12631,11 @@
           <t>072-837-641 87</t>
         </is>
       </c>
-      <c r="E128" s="49" t="n"/>
+      <c r="E128" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F128" s="50" t="n"/>
       <c r="G128" s="51" t="inlineStr">
         <is>
@@ -12219,7 +12723,11 @@
           <t>019-127-850 48</t>
         </is>
       </c>
-      <c r="E129" s="49" t="n"/>
+      <c r="E129" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F129" s="50" t="n"/>
       <c r="G129" s="51" t="inlineStr">
         <is>
@@ -12307,7 +12815,11 @@
           <t>195-688-598 63</t>
         </is>
       </c>
-      <c r="E130" s="49" t="n"/>
+      <c r="E130" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F130" s="50" t="n"/>
       <c r="G130" s="51" t="inlineStr">
         <is>
@@ -12395,7 +12907,11 @@
           <t>119-562-041 56</t>
         </is>
       </c>
-      <c r="E131" s="49" t="n"/>
+      <c r="E131" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F131" s="50" t="n"/>
       <c r="G131" s="51" t="inlineStr">
         <is>
@@ -12483,7 +12999,11 @@
           <t>003-360-060 81</t>
         </is>
       </c>
-      <c r="E132" s="49" t="n"/>
+      <c r="E132" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F132" s="50" t="n"/>
       <c r="G132" s="51" t="inlineStr">
         <is>
@@ -12579,7 +13099,11 @@
           <t>171-022-712 14</t>
         </is>
       </c>
-      <c r="E133" s="49" t="n"/>
+      <c r="E133" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F133" s="50" t="n"/>
       <c r="G133" s="51" t="inlineStr">
         <is>
@@ -12675,7 +13199,11 @@
           <t>001-565-599 28</t>
         </is>
       </c>
-      <c r="E134" s="49" t="n"/>
+      <c r="E134" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F134" s="50" t="n"/>
       <c r="G134" s="51" t="inlineStr">
         <is>
@@ -12771,7 +13299,11 @@
           <t>220-998-823 95</t>
         </is>
       </c>
-      <c r="E135" s="49" t="n"/>
+      <c r="E135" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F135" s="50" t="n"/>
       <c r="G135" s="51" t="inlineStr">
         <is>
@@ -12859,7 +13391,11 @@
           <t>212-785-886 87</t>
         </is>
       </c>
-      <c r="E136" s="49" t="n"/>
+      <c r="E136" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F136" s="50" t="n"/>
       <c r="G136" s="51" t="inlineStr">
         <is>
@@ -12947,7 +13483,11 @@
           <t>106-022-515 91</t>
         </is>
       </c>
-      <c r="E137" s="49" t="n"/>
+      <c r="E137" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F137" s="50" t="n"/>
       <c r="G137" s="51" t="inlineStr">
         <is>
@@ -13043,7 +13583,11 @@
           <t>210-586-598 60</t>
         </is>
       </c>
-      <c r="E138" s="49" t="n"/>
+      <c r="E138" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F138" s="50" t="n"/>
       <c r="G138" s="51" t="inlineStr">
         <is>
@@ -13131,7 +13675,11 @@
           <t>052-280-369 35</t>
         </is>
       </c>
-      <c r="E139" s="49" t="n"/>
+      <c r="E139" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F139" s="50" t="n"/>
       <c r="G139" s="51" t="inlineStr">
         <is>
@@ -13227,7 +13775,11 @@
           <t>141-523-358 26</t>
         </is>
       </c>
-      <c r="E140" s="49" t="n"/>
+      <c r="E140" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F140" s="50" t="n"/>
       <c r="G140" s="51" t="inlineStr">
         <is>
@@ -13315,7 +13867,11 @@
           <t>192-312-367 53</t>
         </is>
       </c>
-      <c r="E141" s="49" t="n"/>
+      <c r="E141" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F141" s="50" t="n"/>
       <c r="G141" s="51" t="inlineStr">
         <is>
@@ -13403,7 +13959,11 @@
           <t>004-366-161 15</t>
         </is>
       </c>
-      <c r="E142" s="49" t="n"/>
+      <c r="E142" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F142" s="50" t="n"/>
       <c r="G142" s="51" t="inlineStr">
         <is>
@@ -13491,7 +14051,11 @@
           <t>198-503-440 98</t>
         </is>
       </c>
-      <c r="E143" s="49" t="n"/>
+      <c r="E143" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F143" s="50" t="n"/>
       <c r="G143" s="51" t="inlineStr">
         <is>
@@ -13579,7 +14143,11 @@
           <t>024-184-963 47</t>
         </is>
       </c>
-      <c r="E144" s="49" t="n"/>
+      <c r="E144" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F144" s="50" t="n"/>
       <c r="G144" s="51" t="inlineStr">
         <is>
@@ -13667,7 +14235,11 @@
           <t>023-445-725 30</t>
         </is>
       </c>
-      <c r="E145" s="49" t="n"/>
+      <c r="E145" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F145" s="50" t="n"/>
       <c r="G145" s="51" t="inlineStr">
         <is>
@@ -13755,7 +14327,11 @@
           <t>105-875-041 55</t>
         </is>
       </c>
-      <c r="E146" s="49" t="n"/>
+      <c r="E146" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F146" s="50" t="n"/>
       <c r="G146" s="51" t="inlineStr">
         <is>
@@ -13851,7 +14427,11 @@
           <t>097-033-687 88</t>
         </is>
       </c>
-      <c r="E147" s="49" t="n"/>
+      <c r="E147" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F147" s="50" t="n"/>
       <c r="G147" s="51" t="inlineStr">
         <is>
@@ -13947,7 +14527,11 @@
           <t>038-809-902 92</t>
         </is>
       </c>
-      <c r="E148" s="49" t="n"/>
+      <c r="E148" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F148" s="50" t="n"/>
       <c r="G148" s="51" t="inlineStr">
         <is>
@@ -14043,7 +14627,11 @@
           <t>192-436-177 81</t>
         </is>
       </c>
-      <c r="E149" s="49" t="n"/>
+      <c r="E149" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F149" s="50" t="n"/>
       <c r="G149" s="51" t="inlineStr">
         <is>
@@ -14139,7 +14727,11 @@
           <t>063-582-034 56</t>
         </is>
       </c>
-      <c r="E150" s="49" t="n"/>
+      <c r="E150" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F150" s="50" t="n"/>
       <c r="G150" s="51" t="inlineStr">
         <is>
@@ -14227,7 +14819,11 @@
           <t>071-662-070 50</t>
         </is>
       </c>
-      <c r="E151" s="49" t="n"/>
+      <c r="E151" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F151" s="50" t="n"/>
       <c r="G151" s="51" t="inlineStr">
         <is>
@@ -14315,7 +14911,11 @@
           <t>042-780-361 49</t>
         </is>
       </c>
-      <c r="E152" s="49" t="n"/>
+      <c r="E152" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F152" s="50" t="n"/>
       <c r="G152" s="51" t="inlineStr">
         <is>
@@ -14403,7 +15003,11 @@
           <t>118-488-714 95</t>
         </is>
       </c>
-      <c r="E153" s="49" t="n"/>
+      <c r="E153" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F153" s="50" t="n"/>
       <c r="G153" s="51" t="inlineStr">
         <is>
@@ -14491,7 +15095,11 @@
           <t>001-499-520 30</t>
         </is>
       </c>
-      <c r="E154" s="49" t="n"/>
+      <c r="E154" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F154" s="50" t="n"/>
       <c r="G154" s="51" t="inlineStr">
         <is>
@@ -14579,7 +15187,11 @@
           <t>172-961-460 90</t>
         </is>
       </c>
-      <c r="E155" s="49" t="n"/>
+      <c r="E155" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F155" s="50" t="n"/>
       <c r="G155" s="51" t="inlineStr">
         <is>
@@ -14667,7 +15279,11 @@
           <t>001-428-997 24</t>
         </is>
       </c>
-      <c r="E156" s="49" t="n"/>
+      <c r="E156" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F156" s="50" t="n"/>
       <c r="G156" s="51" t="inlineStr">
         <is>
@@ -14755,7 +15371,11 @@
           <t>110-851-697 36</t>
         </is>
       </c>
-      <c r="E157" s="49" t="n"/>
+      <c r="E157" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F157" s="50" t="n"/>
       <c r="G157" s="51" t="inlineStr">
         <is>
@@ -14843,7 +15463,11 @@
           <t>030-708-026 07</t>
         </is>
       </c>
-      <c r="E158" s="49" t="n"/>
+      <c r="E158" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F158" s="50" t="n"/>
       <c r="G158" s="51" t="inlineStr">
         <is>
@@ -14931,7 +15555,11 @@
           <t>038-864-601 92</t>
         </is>
       </c>
-      <c r="E159" s="49" t="n"/>
+      <c r="E159" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F159" s="50" t="n"/>
       <c r="G159" s="51" t="inlineStr">
         <is>
@@ -15019,7 +15647,11 @@
           <t>118-093-421 46</t>
         </is>
       </c>
-      <c r="E160" s="49" t="n"/>
+      <c r="E160" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F160" s="50" t="n"/>
       <c r="G160" s="51" t="inlineStr">
         <is>
@@ -15107,7 +15739,11 @@
           <t>109-219-547 54</t>
         </is>
       </c>
-      <c r="E161" s="49" t="n"/>
+      <c r="E161" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F161" s="50" t="n"/>
       <c r="G161" s="51" t="inlineStr">
         <is>
@@ -15195,7 +15831,11 @@
           <t>135-651-925 68</t>
         </is>
       </c>
-      <c r="E162" s="49" t="n"/>
+      <c r="E162" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F162" s="50" t="n"/>
       <c r="G162" s="51" t="inlineStr">
         <is>
@@ -15283,7 +15923,11 @@
           <t>134-348-484 62</t>
         </is>
       </c>
-      <c r="E163" s="49" t="n"/>
+      <c r="E163" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F163" s="50" t="n"/>
       <c r="G163" s="51" t="inlineStr">
         <is>
@@ -15371,7 +16015,11 @@
           <t>187-870-897 52</t>
         </is>
       </c>
-      <c r="E164" s="49" t="n"/>
+      <c r="E164" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F164" s="50" t="n"/>
       <c r="G164" s="51" t="inlineStr">
         <is>
@@ -15459,7 +16107,11 @@
           <t>195-171-820 88</t>
         </is>
       </c>
-      <c r="E165" s="49" t="n"/>
+      <c r="E165" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F165" s="50" t="n"/>
       <c r="G165" s="51" t="inlineStr">
         <is>
@@ -15547,7 +16199,11 @@
           <t>112-495-624 45</t>
         </is>
       </c>
-      <c r="E166" s="49" t="n"/>
+      <c r="E166" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F166" s="50" t="n"/>
       <c r="G166" s="51" t="inlineStr">
         <is>
@@ -15635,7 +16291,11 @@
           <t>027-659-219 78</t>
         </is>
       </c>
-      <c r="E167" s="49" t="n"/>
+      <c r="E167" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F167" s="50" t="n"/>
       <c r="G167" s="51" t="inlineStr">
         <is>
@@ -15723,7 +16383,11 @@
           <t>134-855-108 64</t>
         </is>
       </c>
-      <c r="E168" s="49" t="n"/>
+      <c r="E168" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F168" s="50" t="n"/>
       <c r="G168" s="51" t="inlineStr">
         <is>
@@ -15811,7 +16475,11 @@
           <t>037-460-182 47</t>
         </is>
       </c>
-      <c r="E169" s="49" t="n"/>
+      <c r="E169" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F169" s="50" t="n"/>
       <c r="G169" s="51" t="inlineStr">
         <is>
@@ -15899,7 +16567,11 @@
           <t>038-836-561 94</t>
         </is>
       </c>
-      <c r="E170" s="49" t="n"/>
+      <c r="E170" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F170" s="50" t="n"/>
       <c r="G170" s="51" t="inlineStr">
         <is>
@@ -15987,7 +16659,11 @@
           <t>041-135-891 22</t>
         </is>
       </c>
-      <c r="E171" s="49" t="n"/>
+      <c r="E171" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F171" s="50" t="n"/>
       <c r="G171" s="51" t="inlineStr">
         <is>
@@ -16075,7 +16751,11 @@
           <t>179-812-577 23</t>
         </is>
       </c>
-      <c r="E172" s="49" t="n"/>
+      <c r="E172" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F172" s="50" t="n"/>
       <c r="G172" s="51" t="inlineStr">
         <is>
@@ -16163,7 +16843,11 @@
           <t>193-533-904 89</t>
         </is>
       </c>
-      <c r="E173" s="49" t="n"/>
+      <c r="E173" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F173" s="50" t="n"/>
       <c r="G173" s="51" t="inlineStr">
         <is>
@@ -16251,7 +16935,11 @@
           <t>056-468-953 06</t>
         </is>
       </c>
-      <c r="E174" s="49" t="n"/>
+      <c r="E174" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F174" s="50" t="n"/>
       <c r="G174" s="51" t="inlineStr">
         <is>
@@ -16339,7 +17027,11 @@
           <t>173-009-514 42</t>
         </is>
       </c>
-      <c r="E175" s="49" t="n"/>
+      <c r="E175" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F175" s="50" t="n"/>
       <c r="G175" s="51" t="inlineStr">
         <is>
@@ -16427,7 +17119,11 @@
           <t>207-658-166 80</t>
         </is>
       </c>
-      <c r="E176" s="49" t="n"/>
+      <c r="E176" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F176" s="50" t="n"/>
       <c r="G176" s="51" t="inlineStr">
         <is>
@@ -16515,7 +17211,11 @@
           <t>076-896-465 42</t>
         </is>
       </c>
-      <c r="E177" s="49" t="n"/>
+      <c r="E177" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F177" s="50" t="n"/>
       <c r="G177" s="51" t="inlineStr">
         <is>
@@ -16603,7 +17303,11 @@
           <t>146-724-576 85</t>
         </is>
       </c>
-      <c r="E178" s="49" t="n"/>
+      <c r="E178" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F178" s="50" t="n"/>
       <c r="G178" s="51" t="inlineStr">
         <is>
@@ -16691,7 +17395,11 @@
           <t>079-329-368 10</t>
         </is>
       </c>
-      <c r="E179" s="49" t="n"/>
+      <c r="E179" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F179" s="50" t="n"/>
       <c r="G179" s="51" t="inlineStr">
         <is>
@@ -16779,7 +17487,11 @@
           <t>157-610-031 45</t>
         </is>
       </c>
-      <c r="E180" s="49" t="n"/>
+      <c r="E180" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F180" s="50" t="n"/>
       <c r="G180" s="51" t="inlineStr">
         <is>
@@ -16867,7 +17579,11 @@
           <t>067-559-164 05</t>
         </is>
       </c>
-      <c r="E181" s="49" t="n"/>
+      <c r="E181" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F181" s="50" t="n"/>
       <c r="G181" s="51" t="inlineStr">
         <is>
@@ -16955,7 +17671,11 @@
           <t>061-620-141 12</t>
         </is>
       </c>
-      <c r="E182" s="49" t="n"/>
+      <c r="E182" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F182" s="50" t="n"/>
       <c r="G182" s="51" t="inlineStr">
         <is>
@@ -17043,7 +17763,11 @@
           <t>123-797-630 84</t>
         </is>
       </c>
-      <c r="E183" s="49" t="n"/>
+      <c r="E183" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F183" s="50" t="n"/>
       <c r="G183" s="51" t="inlineStr">
         <is>
@@ -17131,7 +17855,11 @@
           <t>164-961-104 79</t>
         </is>
       </c>
-      <c r="E184" s="49" t="n"/>
+      <c r="E184" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F184" s="50" t="n"/>
       <c r="G184" s="51" t="inlineStr">
         <is>
@@ -17219,7 +17947,11 @@
           <t>123-371-997 54</t>
         </is>
       </c>
-      <c r="E185" s="49" t="n"/>
+      <c r="E185" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F185" s="50" t="n"/>
       <c r="G185" s="51" t="inlineStr">
         <is>
@@ -17307,7 +18039,11 @@
           <t>095-257-608 97</t>
         </is>
       </c>
-      <c r="E186" s="49" t="n"/>
+      <c r="E186" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F186" s="50" t="n"/>
       <c r="G186" s="51" t="inlineStr">
         <is>
@@ -17395,7 +18131,11 @@
           <t>135-472-404 50</t>
         </is>
       </c>
-      <c r="E187" s="49" t="n"/>
+      <c r="E187" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F187" s="50" t="n"/>
       <c r="G187" s="51" t="inlineStr">
         <is>
@@ -17483,7 +18223,11 @@
           <t>062-969-478 14</t>
         </is>
       </c>
-      <c r="E188" s="49" t="n"/>
+      <c r="E188" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F188" s="50" t="n"/>
       <c r="G188" s="51" t="inlineStr">
         <is>
@@ -17571,7 +18315,11 @@
           <t>035-995-049 94</t>
         </is>
       </c>
-      <c r="E189" s="49" t="n"/>
+      <c r="E189" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F189" s="50" t="n"/>
       <c r="G189" s="51" t="inlineStr">
         <is>
@@ -17659,7 +18407,11 @@
           <t>126-987-347 11</t>
         </is>
       </c>
-      <c r="E190" s="49" t="n"/>
+      <c r="E190" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F190" s="50" t="n"/>
       <c r="G190" s="51" t="inlineStr">
         <is>
@@ -17747,7 +18499,11 @@
           <t>145-019-092 36</t>
         </is>
       </c>
-      <c r="E191" s="49" t="n"/>
+      <c r="E191" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F191" s="50" t="n"/>
       <c r="G191" s="51" t="inlineStr">
         <is>
@@ -17835,7 +18591,11 @@
           <t>052-011-489 00</t>
         </is>
       </c>
-      <c r="E192" s="49" t="n"/>
+      <c r="E192" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F192" s="50" t="n"/>
       <c r="G192" s="51" t="inlineStr">
         <is>
@@ -17923,7 +18683,11 @@
           <t>122-075-617 20</t>
         </is>
       </c>
-      <c r="E193" s="49" t="n"/>
+      <c r="E193" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F193" s="50" t="n"/>
       <c r="G193" s="51" t="inlineStr">
         <is>
@@ -18011,7 +18775,11 @@
           <t>117-452-085 43</t>
         </is>
       </c>
-      <c r="E194" s="49" t="n"/>
+      <c r="E194" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F194" s="50" t="n"/>
       <c r="G194" s="51" t="inlineStr">
         <is>
@@ -18099,7 +18867,11 @@
           <t>001-525-262 87</t>
         </is>
       </c>
-      <c r="E195" s="49" t="n"/>
+      <c r="E195" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F195" s="50" t="n"/>
       <c r="G195" s="51" t="inlineStr">
         <is>
@@ -18187,7 +18959,11 @@
           <t>149-051-996 83</t>
         </is>
       </c>
-      <c r="E196" s="49" t="n"/>
+      <c r="E196" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F196" s="50" t="n"/>
       <c r="G196" s="51" t="inlineStr">
         <is>
@@ -18275,7 +19051,11 @@
           <t>068-677-920 32</t>
         </is>
       </c>
-      <c r="E197" s="49" t="n"/>
+      <c r="E197" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F197" s="50" t="n"/>
       <c r="G197" s="51" t="inlineStr">
         <is>
@@ -18363,7 +19143,11 @@
           <t>110-735-963 35</t>
         </is>
       </c>
-      <c r="E198" s="49" t="n"/>
+      <c r="E198" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F198" s="50" t="n"/>
       <c r="G198" s="51" t="inlineStr">
         <is>
@@ -18451,7 +19235,11 @@
           <t>106-689-527 88</t>
         </is>
       </c>
-      <c r="E199" s="49" t="n"/>
+      <c r="E199" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F199" s="50" t="n"/>
       <c r="G199" s="51" t="inlineStr">
         <is>
@@ -18539,7 +19327,11 @@
           <t>143-266-272 49</t>
         </is>
       </c>
-      <c r="E200" s="49" t="n"/>
+      <c r="E200" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F200" s="50" t="n"/>
       <c r="G200" s="51" t="inlineStr">
         <is>
@@ -18627,7 +19419,11 @@
           <t>167-936-806 27</t>
         </is>
       </c>
-      <c r="E201" s="49" t="n"/>
+      <c r="E201" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F201" s="50" t="n"/>
       <c r="G201" s="51" t="inlineStr">
         <is>
@@ -18715,7 +19511,11 @@
           <t>144-685-068 84</t>
         </is>
       </c>
-      <c r="E202" s="49" t="n"/>
+      <c r="E202" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F202" s="50" t="n"/>
       <c r="G202" s="51" t="inlineStr">
         <is>
@@ -18803,7 +19603,11 @@
           <t>064-564-206 63</t>
         </is>
       </c>
-      <c r="E203" s="49" t="n"/>
+      <c r="E203" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F203" s="50" t="n"/>
       <c r="G203" s="51" t="inlineStr">
         <is>
@@ -18891,7 +19695,11 @@
           <t>164-342-983 76</t>
         </is>
       </c>
-      <c r="E204" s="49" t="n"/>
+      <c r="E204" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F204" s="50" t="n"/>
       <c r="G204" s="51" t="inlineStr">
         <is>
@@ -18979,7 +19787,11 @@
           <t>116-713-887 64</t>
         </is>
       </c>
-      <c r="E205" s="49" t="n"/>
+      <c r="E205" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F205" s="50" t="n"/>
       <c r="G205" s="51" t="inlineStr">
         <is>
@@ -19067,7 +19879,11 @@
           <t>152-559-821 82</t>
         </is>
       </c>
-      <c r="E206" s="49" t="n"/>
+      <c r="E206" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F206" s="50" t="n"/>
       <c r="G206" s="51" t="inlineStr">
         <is>
@@ -19155,7 +19971,11 @@
           <t>173-547-161 79</t>
         </is>
       </c>
-      <c r="E207" s="49" t="n"/>
+      <c r="E207" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F207" s="50" t="n"/>
       <c r="G207" s="51" t="inlineStr">
         <is>
@@ -19243,7 +20063,11 @@
           <t>019-124-361 24</t>
         </is>
       </c>
-      <c r="E208" s="49" t="n"/>
+      <c r="E208" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F208" s="50" t="n"/>
       <c r="G208" s="51" t="inlineStr">
         <is>
@@ -19331,7 +20155,11 @@
           <t>112-436-131 03</t>
         </is>
       </c>
-      <c r="E209" s="49" t="n"/>
+      <c r="E209" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F209" s="50" t="n"/>
       <c r="G209" s="51" t="inlineStr">
         <is>
@@ -19419,7 +20247,11 @@
           <t>123-446-092 33</t>
         </is>
       </c>
-      <c r="E210" s="49" t="n"/>
+      <c r="E210" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F210" s="50" t="n"/>
       <c r="G210" s="51" t="inlineStr">
         <is>
@@ -19507,7 +20339,11 @@
           <t>017-273-436 39</t>
         </is>
       </c>
-      <c r="E211" s="49" t="n"/>
+      <c r="E211" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F211" s="50" t="n"/>
       <c r="G211" s="51" t="inlineStr">
         <is>
@@ -19595,7 +20431,11 @@
           <t>140-699-679 98</t>
         </is>
       </c>
-      <c r="E212" s="49" t="n"/>
+      <c r="E212" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F212" s="50" t="n"/>
       <c r="G212" s="51" t="inlineStr">
         <is>
@@ -19683,7 +20523,11 @@
           <t>171-022-713 15</t>
         </is>
       </c>
-      <c r="E213" s="49" t="n"/>
+      <c r="E213" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F213" s="50" t="n"/>
       <c r="G213" s="51" t="inlineStr">
         <is>
@@ -19771,7 +20615,11 @@
           <t>128-046-255 45</t>
         </is>
       </c>
-      <c r="E214" s="49" t="n"/>
+      <c r="E214" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F214" s="50" t="n"/>
       <c r="G214" s="51" t="inlineStr">
         <is>
@@ -19859,7 +20707,11 @@
           <t>137-939-293 12</t>
         </is>
       </c>
-      <c r="E215" s="49" t="n"/>
+      <c r="E215" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F215" s="50" t="n"/>
       <c r="G215" s="51" t="inlineStr">
         <is>
@@ -19947,7 +20799,11 @@
           <t>044-054-282 24</t>
         </is>
       </c>
-      <c r="E216" s="49" t="n"/>
+      <c r="E216" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F216" s="50" t="n"/>
       <c r="G216" s="51" t="inlineStr">
         <is>
@@ -20035,7 +20891,11 @@
           <t>071-694-847 98</t>
         </is>
       </c>
-      <c r="E217" s="49" t="n"/>
+      <c r="E217" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F217" s="50" t="n"/>
       <c r="G217" s="51" t="inlineStr">
         <is>
@@ -20123,7 +20983,11 @@
           <t>126-547-755 80</t>
         </is>
       </c>
-      <c r="E218" s="49" t="n"/>
+      <c r="E218" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F218" s="50" t="n"/>
       <c r="G218" s="51" t="inlineStr">
         <is>
@@ -20211,7 +21075,11 @@
           <t>077-826-209 00</t>
         </is>
       </c>
-      <c r="E219" s="49" t="n"/>
+      <c r="E219" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F219" s="50" t="n"/>
       <c r="G219" s="51" t="inlineStr">
         <is>
@@ -20299,7 +21167,11 @@
           <t>068-782-527 18</t>
         </is>
       </c>
-      <c r="E220" s="49" t="n"/>
+      <c r="E220" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F220" s="50" t="n"/>
       <c r="G220" s="51" t="inlineStr">
         <is>
@@ -20387,7 +21259,11 @@
           <t>133-055-324 15</t>
         </is>
       </c>
-      <c r="E221" s="49" t="n"/>
+      <c r="E221" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F221" s="50" t="n"/>
       <c r="G221" s="51" t="n"/>
       <c r="H221" s="49" t="n"/>
@@ -20479,7 +21355,11 @@
           <t>137-353-721 62</t>
         </is>
       </c>
-      <c r="E222" s="49" t="n"/>
+      <c r="E222" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F222" s="50" t="n"/>
       <c r="G222" s="51" t="n"/>
       <c r="H222" s="49" t="n"/>
@@ -20571,7 +21451,11 @@
           <t>165-320-758 58</t>
         </is>
       </c>
-      <c r="E223" s="49" t="n"/>
+      <c r="E223" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F223" s="50" t="n"/>
       <c r="G223" s="51" t="n"/>
       <c r="H223" s="49" t="n"/>
@@ -20663,7 +21547,11 @@
           <t>114-455-402 27</t>
         </is>
       </c>
-      <c r="E224" s="49" t="n"/>
+      <c r="E224" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F224" s="50" t="n"/>
       <c r="G224" s="51" t="n"/>
       <c r="H224" s="49" t="n"/>
@@ -20755,7 +21643,11 @@
           <t>053-851-554 66</t>
         </is>
       </c>
-      <c r="E225" s="49" t="n"/>
+      <c r="E225" s="46" t="inlineStr">
+        <is>
+          <t>РФ</t>
+        </is>
+      </c>
       <c r="F225" s="50" t="n"/>
       <c r="G225" s="51" t="n"/>
       <c r="H225" s="49" t="n"/>
